--- a/MU/Test upload format/Normal/2027 - 2028/Q4 27-28.xlsx
+++ b/MU/Test upload format/Normal/2027 - 2028/Q4 27-28.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>Q4CR701new</t>
+    <t>Q4CR901new</t>
   </si>
   <si>
     <t>900000</t>
@@ -212,7 +212,7 @@
     <t>SBIN0001234</t>
   </si>
   <si>
-    <t>Q4CR702new</t>
+    <t>Q4CR902new</t>
   </si>
   <si>
     <t>800000</t>
@@ -230,7 +230,7 @@
     <t>CR703</t>
   </si>
   <si>
-    <t>Q4CR703new</t>
+    <t>Q4CR903new</t>
   </si>
   <si>
     <t>500000</t>
@@ -248,7 +248,7 @@
     <t>CR704</t>
   </si>
   <si>
-    <t>Q4CR704new</t>
+    <t>Q4CR904new</t>
   </si>
   <si>
     <t>100000</t>
@@ -257,67 +257,67 @@
     <t>CR705</t>
   </si>
   <si>
-    <t>Q4CR705new</t>
+    <t>Q4CR905new</t>
   </si>
   <si>
     <t>CR706</t>
   </si>
   <si>
-    <t>Q4CR706new</t>
+    <t>Q4CR906new</t>
   </si>
   <si>
     <t>CR707</t>
   </si>
   <si>
-    <t>Q4CR707new</t>
+    <t>Q4CR907new</t>
   </si>
   <si>
     <t>CR708</t>
   </si>
   <si>
-    <t>Q4CR708new</t>
+    <t>Q4CR908new</t>
   </si>
   <si>
     <t>CR709</t>
   </si>
   <si>
-    <t>Q4CR709new</t>
+    <t>Q4CR909new</t>
   </si>
   <si>
     <t>CR710</t>
   </si>
   <si>
-    <t>Q4CR710new</t>
+    <t>Q4CR910new</t>
   </si>
   <si>
     <t>CR711</t>
   </si>
   <si>
-    <t>Q4CR711new</t>
+    <t>Q4CR911new</t>
   </si>
   <si>
     <t>CR712</t>
   </si>
   <si>
-    <t>Q4CR712new</t>
+    <t>Q4CR912new</t>
   </si>
   <si>
     <t>CR713</t>
   </si>
   <si>
-    <t>Q4CR713new</t>
+    <t>Q4CR913new</t>
   </si>
   <si>
     <t>CR714</t>
   </si>
   <si>
-    <t>Q4CR714new</t>
+    <t>Q4CR914new</t>
   </si>
   <si>
     <t>CR715</t>
   </si>
   <si>
-    <t>Q4CR715new</t>
+    <t>Q4CR915new</t>
   </si>
   <si>
     <t>3</t>
@@ -326,7 +326,7 @@
     <t>CR716</t>
   </si>
   <si>
-    <t>Q4CR716new</t>
+    <t>Q4CR916new</t>
   </si>
   <si>
     <t>4</t>
@@ -335,7 +335,7 @@
     <t>CR717</t>
   </si>
   <si>
-    <t>Q4CR717new</t>
+    <t>Q4CR917new</t>
   </si>
   <si>
     <t>TP</t>
@@ -344,7 +344,7 @@
     <t>CR718</t>
   </si>
   <si>
-    <t>Q4CR718new</t>
+    <t>Q4CR918new</t>
   </si>
   <si>
     <t>1000000</t>
@@ -356,37 +356,37 @@
     <t>CR719</t>
   </si>
   <si>
-    <t>Q4CR719new</t>
+    <t>Q4CR919new</t>
   </si>
   <si>
     <t>CR720</t>
   </si>
   <si>
-    <t>Q4CR720new</t>
+    <t>Q4CR920new</t>
   </si>
   <si>
     <t>CR721</t>
   </si>
   <si>
-    <t>Q4CR721new</t>
+    <t>Q4CR921new</t>
   </si>
   <si>
     <t>CR722</t>
   </si>
   <si>
-    <t>Q4CR722new</t>
+    <t>Q4CR922new</t>
   </si>
   <si>
     <t>CR723</t>
   </si>
   <si>
-    <t>Q4CR723new</t>
+    <t>Q4CR923new</t>
   </si>
   <si>
     <t>CR724</t>
   </si>
   <si>
-    <t>Q4CR724new</t>
+    <t>Q4CR924new</t>
   </si>
 </sst>
 </file>
@@ -4237,7 +4237,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="P12:P25">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12:Q25">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
